--- a/artfynd/S 811-2025 artfynd.xlsx
+++ b/artfynd/S 811-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112254741</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111579485</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148531</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129576608</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1269,6 +1294,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129576610</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1375,8 +1405,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86581827</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 811-2025 artfynd.xlsx
+++ b/artfynd/S 811-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,56 +680,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112254741</v>
+        <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>99646</v>
+        <v>107650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222541</v>
+        <v>626</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Ljungögontröst</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Juncus squarrosus</t>
+          <t>Euphrasia micrantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Rchb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flyet mot O, Hl</t>
+          <t>Övraböke, 1240 m NO, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372882</v>
+        <v>373423</v>
       </c>
       <c r="R2" t="n">
-        <v>6311195</v>
+        <v>6311153</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,14 +759,19 @@
           <t>Slättåkra</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>N-Hal-2067</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,81 +784,80 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Skogsväg grus fukt</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Arne Lysell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112254741</t>
+          <t>https://artportalen.se/Sighting/135593686</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111579485</v>
+        <v>112254741</v>
       </c>
       <c r="B3" t="n">
-        <v>98194</v>
+        <v>99646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>222541</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Juncus squarrosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hasselbråten mot O2, Hl</t>
+          <t>Flyet mot O, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>373468</v>
+        <v>372882</v>
       </c>
       <c r="R3" t="n">
-        <v>6298285</v>
+        <v>6311195</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,17 +876,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Enslöv</t>
+          <t>Slättåkra</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +901,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Granåker kärr</t>
+          <t>Skogsväg grus fukt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -906,60 +918,59 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111579485</t>
+          <t>https://artportalen.se/Sighting/112254741</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127148531</v>
+        <v>111579485</v>
       </c>
       <c r="B4" t="n">
-        <v>102171</v>
+        <v>98194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>692</v>
+        <v>220686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hårginst</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Genista pilosa</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Moaslätten, Hl</t>
+          <t>Hasselbråten mot O2, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>375068</v>
+        <v>373468</v>
       </c>
       <c r="R4" t="n">
-        <v>6294855</v>
+        <v>6298285</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,17 +997,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka förekomst</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,47 +1011,39 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Ytterslänt</t>
+          <t>Granåker kärr</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gabriella Samuelsson</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gabriella Samuelsson, Rasmus Andgren Ullberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127148531</t>
+          <t>https://artportalen.se/Sighting/111579485</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129576608</v>
+        <v>127148531</v>
       </c>
       <c r="B5" t="n">
-        <v>102170</v>
+        <v>102171</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375204</v>
+        <v>375068</v>
       </c>
       <c r="R5" t="n">
-        <v>6295182</v>
+        <v>6294855</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,7 +1124,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Enstaka förekomst</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,13 +1164,13 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129576608</t>
+          <t>https://artportalen.se/Sighting/127148531</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129576610</v>
+        <v>129576608</v>
       </c>
       <c r="B6" t="n">
         <v>102170</v>
@@ -1202,7 +1200,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1216,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375134</v>
+        <v>375204</v>
       </c>
       <c r="R6" t="n">
-        <v>6294956</v>
+        <v>6295182</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1296,63 +1294,63 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129576610</t>
+          <t>https://artportalen.se/Sighting/129576608</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86581827</v>
+        <v>129576610</v>
       </c>
       <c r="B7" t="n">
-        <v>99153</v>
+        <v>102170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>692</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Hårginst</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Genista pilosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väg 26, Hl</t>
+          <t>Moaslätten, Hl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>375267</v>
+        <v>375134</v>
       </c>
       <c r="R7" t="n">
-        <v>6295310</v>
+        <v>6294956</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,12 +1374,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,20 +1395,145 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Ytterslänt</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gabriella Samuelsson, Rasmus Andgren Ullberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129576610</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>86581827</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Väg 26, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>375267</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6295310</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Fredrik Winterås</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Fredrik Winterås</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr">
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/86581827</t>
         </is>
@@ -1419,6 +1547,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 811-2025 artfynd.xlsx
+++ b/artfynd/S 811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>107650</v>
+        <v>107705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 811-2025 artfynd.xlsx
+++ b/artfynd/S 811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>107705</v>
+        <v>107732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 811-2025 artfynd.xlsx
+++ b/artfynd/S 811-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,56 +680,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112254741</v>
+        <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>99646</v>
+        <v>107737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222541</v>
+        <v>626</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Ljungögontröst</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Juncus squarrosus</t>
+          <t>Euphrasia micrantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Rchb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flyet mot O, Hl</t>
+          <t>Övraböke, 1240 m NO, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372882</v>
+        <v>373423</v>
       </c>
       <c r="R2" t="n">
-        <v>6311195</v>
+        <v>6311153</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,14 +759,19 @@
           <t>Slättåkra</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>N-Hal-2067</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,81 +784,80 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Skogsväg grus fukt</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Arne Lysell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112254741</t>
+          <t>https://artportalen.se/Sighting/135593686</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111579485</v>
+        <v>112254741</v>
       </c>
       <c r="B3" t="n">
-        <v>98194</v>
+        <v>99646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>222541</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Borsttåg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Juncus squarrosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hasselbråten mot O2, Hl</t>
+          <t>Flyet mot O, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>373468</v>
+        <v>372882</v>
       </c>
       <c r="R3" t="n">
-        <v>6298285</v>
+        <v>6311195</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,17 +876,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Enslöv</t>
+          <t>Slättåkra</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +901,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Granåker kärr</t>
+          <t>Skogsväg grus fukt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -906,60 +918,59 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111579485</t>
+          <t>https://artportalen.se/Sighting/112254741</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127148531</v>
+        <v>111579485</v>
       </c>
       <c r="B4" t="n">
-        <v>102171</v>
+        <v>98194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>692</v>
+        <v>220686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hårginst</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Genista pilosa</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Moaslätten, Hl</t>
+          <t>Hasselbråten mot O2, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>375068</v>
+        <v>373468</v>
       </c>
       <c r="R4" t="n">
-        <v>6294855</v>
+        <v>6298285</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,17 +997,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka förekomst</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,47 +1011,39 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Ytterslänt</t>
+          <t>Granåker kärr</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gabriella Samuelsson</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gabriella Samuelsson, Rasmus Andgren Ullberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127148531</t>
+          <t>https://artportalen.se/Sighting/111579485</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129576608</v>
+        <v>127148531</v>
       </c>
       <c r="B5" t="n">
-        <v>102170</v>
+        <v>102171</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375204</v>
+        <v>375068</v>
       </c>
       <c r="R5" t="n">
-        <v>6295182</v>
+        <v>6294855</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,7 +1124,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Enstaka förekomst</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,13 +1164,13 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129576608</t>
+          <t>https://artportalen.se/Sighting/127148531</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129576610</v>
+        <v>129576608</v>
       </c>
       <c r="B6" t="n">
         <v>102170</v>
@@ -1202,7 +1200,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1216,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375134</v>
+        <v>375204</v>
       </c>
       <c r="R6" t="n">
-        <v>6294956</v>
+        <v>6295182</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1296,63 +1294,63 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129576610</t>
+          <t>https://artportalen.se/Sighting/129576608</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86581827</v>
+        <v>129576610</v>
       </c>
       <c r="B7" t="n">
-        <v>99153</v>
+        <v>102170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>692</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Hårginst</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Genista pilosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väg 26, Hl</t>
+          <t>Moaslätten, Hl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>375267</v>
+        <v>375134</v>
       </c>
       <c r="R7" t="n">
-        <v>6295310</v>
+        <v>6294956</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,12 +1374,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,20 +1395,145 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Ytterslänt</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gabriella Samuelsson, Rasmus Andgren Ullberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129576610</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>86581827</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Väg 26, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>375267</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6295310</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Fredrik Winterås</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Fredrik Winterås</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr">
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/86581827</t>
         </is>
@@ -1419,6 +1547,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 811-2025 artfynd.xlsx
+++ b/artfynd/S 811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>107737</v>
+        <v>107739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 811-2025 artfynd.xlsx
+++ b/artfynd/S 811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>107739</v>
+        <v>107762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 811-2025 artfynd.xlsx
+++ b/artfynd/S 811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>107762</v>
+        <v>107764</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 811-2025 artfynd.xlsx
+++ b/artfynd/S 811-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593686</v>
       </c>
       <c r="B2" t="n">
-        <v>107764</v>
+        <v>107765</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
